--- a/AAII_Financials/Yearly/RBGLY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RBGLY_YR_FIN.xlsx
@@ -940,7 +940,7 @@
         <v>1259400</v>
       </c>
       <c r="F14" s="3">
-        <v>1031700</v>
+        <v>866200</v>
       </c>
       <c r="G14" s="3">
         <v>53000</v>
@@ -1127,7 +1127,7 @@
         <v>-1300</v>
       </c>
       <c r="F20" s="3">
-        <v>-157900</v>
+        <v>7600</v>
       </c>
       <c r="G20" s="3">
         <v>55400</v>
@@ -1166,7 +1166,7 @@
         <v>4691000</v>
       </c>
       <c r="F21" s="3">
-        <v>4807200</v>
+        <v>4641600</v>
       </c>
       <c r="G21" s="3">
         <v>4338800</v>
@@ -1595,7 +1595,7 @@
         <v>1300</v>
       </c>
       <c r="F32" s="3">
-        <v>157900</v>
+        <v>-7600</v>
       </c>
       <c r="G32" s="3">
         <v>-55400</v>
